--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId2"/>
@@ -165,7 +165,7 @@
     <t xml:space="preserve">2 x Erni šroubovací svorky M5 PRESSFIT</t>
   </si>
   <si>
-    <t xml:space="preserve">1 x 5pin MOLEX micro-lock, 505570-0401</t>
+    <t xml:space="preserve">1 x 5pin MOLEX micro-lock, 505570-0501</t>
   </si>
   <si>
     <t xml:space="preserve">3 x Erni šroubovací svorky M5 PRESSFIT </t>
@@ -299,7 +299,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.92"/>
@@ -506,7 +506,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
@@ -713,7 +713,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="TGZ-S-48-50_100" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="TGZ-D-48-50_100" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="67">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -150,6 +151,33 @@
     <t xml:space="preserve">1x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
   </si>
   <si>
+    <t xml:space="preserve">4,8 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 50 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 100 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x 1pin WAGO push-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 x 1pin WAGO push-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brzdový konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 × 6pin WEIDMÜLLER  BLF 5.00HC/06/180F</t>
+  </si>
+  <si>
     <t xml:space="preserve">2,4 kW</t>
   </si>
   <si>
@@ -171,34 +199,31 @@
     <t xml:space="preserve">3 x Erni šroubovací svorky M5 PRESSFIT </t>
   </si>
   <si>
-    <t xml:space="preserve">Brzdový konektor</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 x 4pin MOLEX micro-lock, 505570-0501</t>
   </si>
   <si>
-    <t xml:space="preserve">4,8 kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 50 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 100 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 x 1pin WAGO push-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 x 1pin WAGO push-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 × 6pin WEIDMÜLLER  BLF 5.00HC/06/180F</t>
+    <t xml:space="preserve">250 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 x Pressfit M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin MOLEX Micro-Fit 3.0, 436450500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x Pressfit M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin MOLEX Micro-Fit 3.0, 430250400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Externí temistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 2pin MOLEX Micro-Fit 3.0, 430250200</t>
   </si>
 </sst>
 </file>
@@ -276,9 +301,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -299,7 +328,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.92"/>
@@ -505,10 +534,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
   </cols>
   <sheetData>
@@ -554,7 +583,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>44</v>
@@ -562,103 +591,103 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>1</v>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B13" s="0" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B16" s="0" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B20" s="0" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>47</v>
@@ -666,33 +695,41 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B28" s="0" t="s">
         <v>41</v>
       </c>
     </row>
@@ -712,10 +749,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
   </cols>
   <sheetData>
@@ -761,7 +798,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>53</v>
@@ -769,103 +806,103 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>55</v>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="0" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="0" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="0" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>56</v>
@@ -873,42 +910,249 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
         <v>38</v>
       </c>
+      <c r="B26" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
       <c r="B27" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,13 +5,18 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="88">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -224,6 +229,69 @@
   </si>
   <si>
     <t xml:space="preserve">1 x 2pin MOLEX Micro-Fit 3.0, 430250200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">425 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230 VAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,6 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 10pin WEIDMÜLLER  BLZP 5.08HC/10/180  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 6pin WEIDMÜLLER  SLS 5.08/06/180FI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMI FILTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doporučený filtr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLMO62P72-04 nebo NLA062P72-04  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">140-320 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,6 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 10 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 3pin PHOENIX  PC 5/ 3-STCL1-7,62  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 6pin WEIDMÜLLER  SLS 5.08/06/180FI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
   </si>
 </sst>
 </file>
@@ -301,13 +369,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -328,7 +400,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.92"/>
@@ -535,7 +607,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
@@ -750,7 +822,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
@@ -957,7 +1029,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
@@ -1153,6 +1225,1062 @@
       </c>
       <c r="B28" s="0" t="s">
         <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,18 +5,22 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
-    <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="TGZ-S-400-3_9" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="TGZ-S-400-7_15" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="TGZ-S-400-10_20" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="107">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -292,6 +296,63 @@
   </si>
   <si>
     <t xml:space="preserve">2 x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400 VAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,7 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pracovní spínací frekvence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 kHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin WEIDMÜLLER BLZ 7.62HP/12/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 6pin WEIDMÜLLER  BLF 7.62HP/06/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCZXX3P49-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,9 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,6 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,4 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 kHz</t>
   </si>
 </sst>
 </file>
@@ -369,17 +430,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -394,199 +467,305 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -601,207 +780,1171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -817,198 +1960,198 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1024,206 +2167,206 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1239,206 +2382,206 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1454,206 +2597,206 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1669,203 +2812,203 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1881,198 +3024,198 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2088,198 +3231,198 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>77</v>
       </c>
     </row>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,22 +5,23 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
   </bookViews>
   <sheets>
-    <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="TGZ-S-400-3_9" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="TGZ-S-400-7_15" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="TGZ-S-400-10_20" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-S-400-3_9" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="TGZ-S-400-7_15" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="TGZ-S-400-10_20" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="TGZ-D-560-30_50" sheetId="14" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="115">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -175,10 +176,10 @@
     <t xml:space="preserve">50 W</t>
   </si>
   <si>
-    <t xml:space="preserve">3 x 1pin WAGO push-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 x 1pin WAGO push-in</t>
+    <t xml:space="preserve">1 x 3pin WAGO push-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WAGO push-in</t>
   </si>
   <si>
     <t xml:space="preserve">Brzdový konektor</t>
@@ -199,6 +200,9 @@
     <t xml:space="preserve">30 W</t>
   </si>
   <si>
+    <t xml:space="preserve">LED signalizace</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 x Erni šroubovací svorky M5 PRESSFIT</t>
   </si>
   <si>
@@ -353,6 +357,27 @@
   </si>
   <si>
     <t xml:space="preserve">10 kHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-560 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">900 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">šroubovací svorky M8x12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtr obsahující napájecí modul TGS-560</t>
   </si>
 </sst>
 </file>
@@ -447,12 +472,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -467,119 +492,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.92"/>
@@ -781,233 +700,233 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>88</v>
+      <c r="B3" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>89</v>
+      <c r="B4" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>90</v>
+      <c r="B5" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>91</v>
+      <c r="B6" s="4" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="A8" s="4" t="s">
         <v>93</v>
       </c>
+      <c r="B8" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0"/>
-      <c r="B9" s="0"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="A20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>94</v>
+      <c r="B23" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>74</v>
+      <c r="B24" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>95</v>
+      <c r="B25" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>76</v>
+      <c r="B26" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>77</v>
+      <c r="B27" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="0"/>
+      <c r="A29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>96</v>
+      <c r="A30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1022,233 +941,233 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>88</v>
+      <c r="B3" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0"/>
-      <c r="B9" s="0"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1263,233 +1182,233 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>88</v>
+      <c r="B3" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>99</v>
+      <c r="B4" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>100</v>
+      <c r="B5" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>101</v>
+      <c r="B6" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>60</v>
+      <c r="B7" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="A8" s="4" t="s">
         <v>93</v>
       </c>
+      <c r="B8" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0"/>
-      <c r="B9" s="0"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="A20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>94</v>
+      <c r="B23" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>74</v>
+      <c r="B24" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>95</v>
+      <c r="B25" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>76</v>
+      <c r="B26" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>77</v>
+      <c r="B27" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="0"/>
+      <c r="A29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>96</v>
+      <c r="A30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1504,18 +1423,259 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1696,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1544,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1552,31 +1712,31 @@
         <v>8</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1675,12 +1835,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1688,7 +1848,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1696,7 +1856,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1704,7 +1864,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1712,7 +1872,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1721,17 +1881,41 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>96</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0"/>
+      <c r="B32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
+      <c r="B35" s="0"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0"/>
+      <c r="B36" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1745,12 +1929,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -1960,12 +2144,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -2093,7 +2277,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -2112,7 +2296,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2120,7 +2304,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2128,7 +2312,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2136,7 +2320,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2167,12 +2351,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -2223,7 +2407,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2231,7 +2415,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2300,7 +2484,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -2319,7 +2503,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2327,7 +2511,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2335,7 +2519,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2343,7 +2527,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2364,10 +2548,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2382,12 +2566,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -2438,7 +2622,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2446,7 +2630,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2515,7 +2699,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -2534,7 +2718,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2542,7 +2726,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2550,7 +2734,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2558,7 +2742,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2579,10 +2763,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2597,12 +2781,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -2653,7 +2837,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2661,7 +2845,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2730,7 +2914,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -2749,7 +2933,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2757,7 +2941,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2765,7 +2949,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2773,7 +2957,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2794,10 +2978,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2812,12 +2996,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
@@ -2844,7 +3028,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2852,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2860,7 +3044,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2876,7 +3060,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2945,7 +3129,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -2964,7 +3148,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2972,7 +3156,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2980,7 +3164,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2988,7 +3172,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,20 +3180,20 @@
         <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3024,14 +3208,14 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -3056,7 +3240,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3064,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3072,7 +3256,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3080,7 +3264,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,7 +3272,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3184,7 +3368,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3192,7 +3376,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3200,7 +3384,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3208,7 +3392,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3216,7 +3400,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3231,14 +3415,14 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -3263,7 +3447,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3271,7 +3455,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3279,7 +3463,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3287,7 +3471,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3391,7 +3575,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3399,7 +3583,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3407,7 +3591,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3415,7 +3599,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3423,7 +3607,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,23 +5,24 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
   </bookViews>
   <sheets>
-    <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="TGZ-S-400-3_9" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="TGZ-S-400-7_15" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="TGZ-S-400-10_20" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="TGZ-D-560-30_50" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="TGZ-S-400-3_9" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="TGZ-S-400-7_15" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="TGZ-S-400-10_20" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="TGZ-D-560-30_50" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="TGS-320-10_15" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="150">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -371,13 +372,118 @@
     <t xml:space="preserve">900 W</t>
   </si>
   <si>
+    <t xml:space="preserve">VSTUPY/VÝSTUPY</t>
+  </si>
+  <si>
     <t xml:space="preserve">šroubovací svorky M8x12</t>
   </si>
   <si>
     <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180F</t>
   </si>
   <si>
+    <t xml:space="preserve">2 x 4pin  WEIDMÜLLER LSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 8pin WEIDMÜLLER B2CF 3.50/08/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin WEIDMÜLLER B2CF 3.50/12/180</t>
+  </si>
+  <si>
     <t xml:space="preserve">Filtr obsahující napájecí modul TGS-560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vstupní napětí (VAC - 50/60 Hz) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 230 VAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximální vstupní proud (AC) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výstupní napětí (DC) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">320 VDC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximální trvalý výstupní proud (DC) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximální krátkodobý výstupní proud (DC, 1s) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximální výstupní výkon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 200 W </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximální brzdný výkon (interní rezistor) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 W </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximální brzdný výkon (externí rezistor) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 200 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ztráty při maximálním výstupním výkonu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 W </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jištění </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 A (char. Z, dvoupól)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VÝSTUPY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezpotenciálový kontakt RDY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max. 28 VDC / 700 mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezpotenciálový kontakt ERR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x zelená (Ready)  1x červená (Error)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KONEKTORY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Síťový napájecí konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC bus konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 8pin PHOENIX PC 5/ 8-STCL1-7,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konektor pro digitální výstupy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BCZ 3.81/04/180 SN BK BX</t>
   </si>
 </sst>
 </file>
@@ -472,12 +578,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -492,8 +598,114 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -700,7 +912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -925,7 +1137,7 @@
       <c r="A30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -941,7 +1153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1166,7 +1378,7 @@
       <c r="A30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1182,7 +1394,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1407,7 +1619,7 @@
       <c r="A30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1423,7 +1635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1648,7 +1860,7 @@
       <c r="A30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1664,11 +1876,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -1676,6 +1888,235 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -1684,214 +2125,206 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>3</v>
-      </c>
+      <c r="A2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>108</v>
-      </c>
+      <c r="A3" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>109</v>
-      </c>
+      <c r="A4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>105</v>
-      </c>
+      <c r="A5" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>110</v>
-      </c>
+      <c r="A6" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>44</v>
-      </c>
+      <c r="A7" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>111</v>
-      </c>
+      <c r="A8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0"/>
-      <c r="B9" s="0"/>
+      <c r="A9" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>1</v>
-      </c>
+      <c r="A10" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>18</v>
-      </c>
+      <c r="A11" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>20</v>
-      </c>
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
+      <c r="A14" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>25</v>
-      </c>
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>28</v>
-      </c>
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
+      <c r="A21" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>113</v>
-      </c>
+      <c r="A24" s="0"/>
+      <c r="B24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>48</v>
-      </c>
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>88</v>
-      </c>
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>78</v>
-      </c>
+      <c r="A27" s="0"/>
+      <c r="B27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0"/>
       <c r="B28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>79</v>
-      </c>
+      <c r="A29" s="0"/>
       <c r="B29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>114</v>
-      </c>
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0"/>
@@ -1908,14 +2341,6 @@
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0"/>
       <c r="B34" s="0"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0"/>
-      <c r="B35" s="0"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0"/>
-      <c r="B36" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1929,7 +2354,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -2144,7 +2569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -2351,7 +2776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -2566,7 +2991,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -2781,7 +3206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -2996,7 +3421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -3208,7 +3633,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -3415,7 +3840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,6 +23,8 @@
     <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="TGZ-D-560-30_50" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="TGS-320-10_15" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="TGS-560-50_100" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="TGS-560-25_50" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="163">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -480,10 +482,49 @@
     <t xml:space="preserve">1 x 8pin PHOENIX PC 5/ 8-STCL1-7,62</t>
   </si>
   <si>
-    <t xml:space="preserve">Konektor pro digitální výstupy</t>
+    <t xml:space="preserve">Konektor pro kontrolní výstupy</t>
   </si>
   <si>
     <t xml:space="preserve">1 x 4pin WEIDMÜLLER BCZ 3.81/04/180 SN BK BX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x 400 VAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">560 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 7pin WAGO push-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Připojení externího termistoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x 2pin WEIDMÜLLER LSF (push-in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 A</t>
   </si>
 </sst>
 </file>
@@ -2353,6 +2394,522 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0"/>
+      <c r="B27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0"/>
+      <c r="B32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
+      <c r="B35" s="0"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0"/>
+      <c r="B27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0"/>
+      <c r="B32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="16"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,8 +23,8 @@
     <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="TGZ-D-560-30_50" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="TGS-320-10_15" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="TGS-560-50_100" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="TGS-560-25_50" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="TGS-560-25_50" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="TGS-560-50_100" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="164">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -494,9 +494,24 @@
     <t xml:space="preserve">560 VDC</t>
   </si>
   <si>
+    <t xml:space="preserve">25 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 kW</t>
+  </si>
+  <si>
     <t xml:space="preserve">400 W</t>
   </si>
   <si>
+    <t xml:space="preserve">100 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER BCZ 3.81/05/180F</t>
+  </si>
+  <si>
     <t xml:space="preserve">150 W</t>
   </si>
   <si>
@@ -513,18 +528,6 @@
   </si>
   <si>
     <t xml:space="preserve">1x 2pin WEIDMÜLLER LSF (push-in)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 A</t>
   </si>
 </sst>
 </file>
@@ -2399,7 +2402,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2447,7 +2450,7 @@
         <v>125</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C5" s="5"/>
     </row>
@@ -2456,7 +2459,7 @@
         <v>127</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C6" s="5"/>
     </row>
@@ -2465,7 +2468,7 @@
         <v>129</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="C7" s="5"/>
     </row>
@@ -2474,7 +2477,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8" s="5"/>
     </row>
@@ -2492,7 +2495,7 @@
         <v>135</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C10" s="5"/>
     </row>
@@ -2501,7 +2504,7 @@
         <v>137</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C11" s="5"/>
     </row>
@@ -2566,27 +2569,27 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>114</v>
+      <c r="B21" s="0" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>155</v>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>113</v>
+      <c r="B23" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2598,20 +2601,12 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>149</v>
-      </c>
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>158</v>
-      </c>
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0"/>
@@ -2640,14 +2635,6 @@
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0"/>
       <c r="B33" s="0"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0"/>
-      <c r="B34" s="0"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0"/>
-      <c r="B35" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2665,7 +2652,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2713,7 +2700,7 @@
         <v>125</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5"/>
     </row>
@@ -2722,7 +2709,7 @@
         <v>127</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C6" s="5"/>
     </row>
@@ -2731,7 +2718,7 @@
         <v>129</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="C7" s="5"/>
     </row>
@@ -2740,7 +2727,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8" s="5"/>
     </row>
@@ -2758,7 +2745,7 @@
         <v>135</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C10" s="5"/>
     </row>
@@ -2767,7 +2754,7 @@
         <v>137</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C11" s="5"/>
     </row>
@@ -2832,10 +2819,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2843,16 +2830,16 @@
       <c r="A22" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>1</v>
+      <c r="B22" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>1</v>
+      <c r="B23" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2864,12 +2851,20 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
+      <c r="A25" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0"/>
-      <c r="B26" s="0"/>
+      <c r="A26" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0"/>
@@ -2898,6 +2893,14 @@
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0"/>
       <c r="B33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
+      <c r="B35" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,6 +25,7 @@
     <sheet name="TGS-320-10_15" sheetId="15" state="visible" r:id="rId17"/>
     <sheet name="TGS-560-25_50" sheetId="16" state="visible" r:id="rId18"/>
     <sheet name="TGS-560-50_100" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="TGMmini" sheetId="18" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="186">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -528,6 +529,72 @@
   </si>
   <si>
     <t xml:space="preserve">1x 2pin WEIDMÜLLER LSF (push-in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Napájecí napětí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 V DC (± 20 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proudový odběr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min. 1 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Napájení DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethernet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/100 Mbit RJ45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EtherCAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 Mbps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 x USB 2.0, microUSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">microSD slot s detekcí vložené karty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stavová signalizační LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Červená/zelená STS dioda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Napájení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BLF 2.50/04/180 SN BK BX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER B2CF 3.50/04/180 SN OR BX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI/DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 10pin WEIDMÜLLER B2CF 3.50/10/180 SN OR BX</t>
   </si>
 </sst>
 </file>
@@ -605,7 +672,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -623,10 +690,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2152,239 +2215,183 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-    </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-      <c r="B19" s="0"/>
-    </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-      <c r="B24" s="0"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0"/>
-      <c r="B26" s="0"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0"/>
-      <c r="B27" s="0"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0"/>
-      <c r="B30" s="0"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
-      <c r="B31" s="0"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0"/>
-      <c r="B32" s="0"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0"/>
-      <c r="B33" s="0"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0"/>
-      <c r="B34" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2402,239 +2409,191 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5"/>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5"/>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-    </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-      <c r="B19" s="0"/>
-    </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0"/>
-      <c r="B26" s="0"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0"/>
-      <c r="B27" s="0"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0"/>
-      <c r="B30" s="0"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
-      <c r="B31" s="0"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0"/>
-      <c r="B32" s="0"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0"/>
-      <c r="B33" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2652,7 +2611,225 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2669,122 +2846,122 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>119</v>
+      <c r="A2" s="0" t="s">
+        <v>164</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="5"/>
+        <v>165</v>
+      </c>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>121</v>
+      <c r="A3" s="0" t="s">
+        <v>166</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>123</v>
+      <c r="A4" s="0" t="s">
+        <v>168</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="5"/>
+        <v>165</v>
+      </c>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="5"/>
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>127</v>
+      <c r="A6" s="0" t="s">
+        <v>16</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>129</v>
+      <c r="A7" s="0" t="s">
+        <v>169</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>131</v>
+      <c r="A8" s="0" t="s">
+        <v>171</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="5"/>
+        <v>172</v>
+      </c>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>133</v>
+      <c r="A9" s="0" t="s">
+        <v>17</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>135</v>
+      <c r="A10" s="0" t="s">
+        <v>173</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>137</v>
+      <c r="A11" s="0" t="s">
+        <v>175</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" s="5"/>
+        <v>176</v>
+      </c>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
+      <c r="A12" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>1</v>
-      </c>
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>141</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>141</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0"/>
@@ -2792,7 +2969,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>1</v>
@@ -2800,107 +2977,43 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>55</v>
+        <v>181</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-      <c r="B19" s="0"/>
+      <c r="A19" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>160</v>
-      </c>
+      <c r="A22" s="0"/>
+      <c r="B22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="A23" s="0"/>
+      <c r="B23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0"/>
-      <c r="B27" s="0"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0"/>
-      <c r="B30" s="0"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
-      <c r="B31" s="0"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0"/>
-      <c r="B32" s="0"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0"/>
-      <c r="B33" s="0"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0"/>
-      <c r="B34" s="0"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0"/>
-      <c r="B35" s="0"/>
+      <c r="A24" s="0"/>
+      <c r="B24" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="17"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,6 +26,7 @@
     <sheet name="TGS-560-25_50" sheetId="16" state="visible" r:id="rId18"/>
     <sheet name="TGS-560-50_100" sheetId="17" state="visible" r:id="rId19"/>
     <sheet name="TGMmini" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="TGMcontroller" sheetId="19" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="188">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -595,6 +596,12 @@
   </si>
   <si>
     <t xml:space="preserve">2 x 10pin WEIDMÜLLER B2CF 3.50/10/180 SN OR BX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Červená/zelená dioda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 22pin WEIDMÜLLER  B2CF 3.50/22/180</t>
   </si>
 </sst>
 </file>
@@ -2829,7 +2836,185 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2838,182 +3023,160 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0"/>
-      <c r="B5" s="0"/>
       <c r="C5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>170</v>
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>172</v>
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>174</v>
+      <c r="A10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="C10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>176</v>
-      </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>178</v>
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0"/>
+      <c r="A13" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>1</v>
-      </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>180</v>
+      <c r="A15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
+      <c r="A16" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>1</v>
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>182</v>
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>183</v>
+      <c r="A19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0"/>
-      <c r="B22" s="0"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0"/>
-      <c r="B23" s="0"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-      <c r="B24" s="0"/>
+      <c r="A20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="18"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,6 +27,7 @@
     <sheet name="TGS-560-50_100" sheetId="17" state="visible" r:id="rId19"/>
     <sheet name="TGMmini" sheetId="18" state="visible" r:id="rId20"/>
     <sheet name="TGMcontroller" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="TGZpMotion" sheetId="20" state="visible" r:id="rId22"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="188">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -3019,7 +3020,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3404,6 +3405,162 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,29 +5,30 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="19"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="TGZ-S-48-100_250" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="TGZ-S-48-100_300" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="TGZ-S-48-100_425" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="TGZ-S-230-5_15" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="TGZ-D-320-5_10" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="TGZ-D-320-5_15" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="TGZ-S-400-3_9" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="TGZ-S-400-7_15" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="TGZ-S-400-10_20" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="TGZ-S-400-14_30" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="TGZ-D-560-30_50" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="TGS-320-10_15" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="TGS-560-25_50" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="TGS-560-50_100" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="TGMmini" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="TGMcontroller" sheetId="19" state="visible" r:id="rId21"/>
-    <sheet name="TGZpMotion" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="TGZ-S-48-50_100RI" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="TGZ-S-48-100_250" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="TGZ-S-400-3_9" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="TGZ-S-400-7_15" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="TGZ-S-400-10_20" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="TGZ-S-400-14_30" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="TGZ-D-560-30_50" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="TGS-320-10_15" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="TGS-560-25_50" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="TGS-560-50_100" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="TGMmini" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="TGMcontroller" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="TGZpMotion" sheetId="21" state="visible" r:id="rId23"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="208">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -219,6 +220,66 @@
   </si>
   <si>
     <t xml:space="preserve">1 x 4pin MOLEX micro-lock, 505570-0501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100/1000 Mb/s, 2 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100/1000 Mb/s, 1 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I/O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 DI, 6 DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 18pin MOLEX 5031491800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 DI (TTL), 1 AI, 2 PT1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin MOLEX 5031491200 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEEDBACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB1, FB2, FB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x 10pin MOLEX 5031481090 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin MOLEX 5031481290 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC BUS (+DC, -DC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x Pressfit M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Řízení, STO, BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin MOLEX micro-lock, 5055700501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x Pressfit M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Externí teplota, Brzda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin MOLEX Micro-lock 50557005011</t>
   </si>
   <si>
     <t xml:space="preserve">250 A</t>
@@ -680,12 +741,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1031,229 +1100,195 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>89</v>
+      <c r="B3" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>90</v>
+      <c r="B4" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>91</v>
+      <c r="B5" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-    </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-    </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-    </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>96</v>
+      <c r="B25" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>77</v>
+      <c r="B26" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>97</v>
+      <c r="B27" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1280,221 +1315,221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>89</v>
+      <c r="B3" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="4"/>
+      <c r="B29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>97</v>
+      <c r="A30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1521,221 +1556,221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>89</v>
+      <c r="B3" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>97</v>
+      <c r="B30" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1762,221 +1797,221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>89</v>
+      <c r="B3" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>103</v>
+      <c r="B4" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>104</v>
+      <c r="B5" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>105</v>
+      <c r="B6" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>106</v>
+      <c r="B7" s="6" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>107</v>
+      <c r="A8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>96</v>
+      <c r="B25" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>77</v>
+      <c r="B26" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>78</v>
+      <c r="B27" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="4"/>
+      <c r="A29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>97</v>
+      <c r="A30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1995,216 +2030,229 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>108</v>
+      <c r="B3" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>109</v>
+      <c r="B4" s="6" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>105</v>
+      <c r="B5" s="6" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>110</v>
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="A8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+    </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+    </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+    </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="B22" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>113</v>
+      <c r="B23" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>114</v>
+      <c r="B24" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>48</v>
+      <c r="B25" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>115</v>
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>116</v>
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2223,12 +2271,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2240,165 +2287,200 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="4"/>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="4"/>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="4"/>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="4"/>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="4"/>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="4"/>
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="4"/>
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>141</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>143</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>147</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>149</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2417,7 +2499,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2434,98 +2516,98 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="B10" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="4"/>
+      <c r="A11" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
@@ -2533,18 +2615,18 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,12 +2642,12 @@
         <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>1</v>
@@ -2573,34 +2655,26 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2619,7 +2693,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2636,98 +2710,98 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>119</v>
+      <c r="A2" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>170</v>
+      </c>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>121</v>
+      <c r="A3" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>123</v>
+      <c r="A4" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="B8" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="4"/>
+        <v>174</v>
+      </c>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>133</v>
+      <c r="A9" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>135</v>
+      <c r="A10" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>175</v>
+      </c>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>137</v>
+      <c r="A11" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="C11" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
@@ -2735,18 +2809,18 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2762,12 +2836,12 @@
         <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>1</v>
@@ -2778,47 +2852,31 @@
         <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>160</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2837,7 +2895,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2854,122 +2912,122 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>164</v>
+      <c r="A2" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>170</v>
+      </c>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>166</v>
+      <c r="A3" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>168</v>
+      <c r="A4" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>171</v>
+      </c>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="4"/>
+      <c r="A5" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
+      <c r="A6" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>169</v>
+      <c r="A7" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>129</v>
+      </c>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>171</v>
+      <c r="A8" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="4"/>
+        <v>174</v>
+      </c>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
+      <c r="A9" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>173</v>
+      <c r="A10" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>178</v>
+      </c>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>175</v>
+      <c r="A11" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>179</v>
+      </c>
+      <c r="C11" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="4"/>
+      <c r="A13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="4"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
@@ -2977,26 +3035,66 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>185</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3033,33 +3131,33 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>185</v>
+      </c>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="4"/>
+        <v>187</v>
+      </c>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>185</v>
+      </c>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="4"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -3068,25 +3166,25 @@
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>190</v>
+      </c>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="4"/>
+        <v>192</v>
+      </c>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -3095,88 +3193,86 @@
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>194</v>
+      </c>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="4"/>
+      <c r="A11" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="4"/>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C15" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>183</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>88</v>
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>78</v>
+      <c r="A20" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3410,12 +3506,192 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3428,33 +3704,33 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>185</v>
+      </c>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="4"/>
+        <v>187</v>
+      </c>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>185</v>
+      </c>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="4"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -3463,7 +3739,7 @@
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -3472,7 +3748,7 @@
       <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -3481,7 +3757,7 @@
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -3490,19 +3766,19 @@
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>196</v>
+      </c>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="4"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -3511,35 +3787,35 @@
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="4"/>
+        <v>206</v>
+      </c>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="4"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3547,7 +3823,7 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3773,7 +4049,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -3809,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3817,7 +4093,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3825,7 +4101,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3833,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3848,29 +4124,29 @@
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
+      <c r="B10" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
+      <c r="B11" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -3878,98 +4154,121 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>55</v>
+      <c r="A19" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>26</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>41</v>
+      <c r="A27" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>67</v>
+      <c r="A28" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4040,7 +4339,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4048,7 +4347,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4136,7 +4435,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4144,15 +4443,15 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>64</v>
+      <c r="B24" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4160,7 +4459,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4181,10 +4480,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4255,7 +4554,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4263,7 +4562,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4351,7 +4650,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4359,15 +4658,15 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>64</v>
+      <c r="B24" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4375,7 +4674,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4396,10 +4695,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4418,7 +4717,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -4446,7 +4745,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4454,7 +4753,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4462,7 +4761,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4470,7 +4769,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4478,7 +4777,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4566,7 +4865,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4574,44 +4873,47 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>76</v>
+      <c r="B24" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>78</v>
+      <c r="B27" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4630,10 +4932,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -4658,7 +4960,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4666,7 +4968,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4674,151 +4976,156 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4865,7 +5172,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4873,7 +5180,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4881,7 +5188,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4889,7 +5196,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4897,7 +5204,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4993,7 +5300,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5001,7 +5308,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,7 +5316,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5017,7 +5324,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5025,7 +5332,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,30 +5,32 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="TGZ-D-48-50_100" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="TGZ-S-48-50_100" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="TGZ-S-48-50_100RI" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="TGZ-S-48-100_250" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="TGZ-S-48-100_300" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="TGZ-S-48-100_425" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="TGZ-S-230-5_15" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="TGZ-D-320-5_10" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="TGZ-D-320-5_15" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="TGZ-S-400-3_9" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="TGZ-S-400-7_15" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="TGZ-S-400-10_20" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="TGZ-S-400-14_30" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="TGZ-D-560-30_50" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="TGS-320-10_15" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="TGS-560-25_50" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="TGS-560-50_100" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="TGMmini" sheetId="19" state="visible" r:id="rId21"/>
-    <sheet name="TGMcontroller" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="TGZpMotion" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="TGZ-S-48-100_250RI" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="TGZ-S-48-100_300RI" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="TGZ-S-48-100_250" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="TGZ-S-400-3_9" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="TGZ-S-400-7_15" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="TGZ-S-400-10_20" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="TGZ-S-400-14_30" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="TGZ-D-560-30_50" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="TGS-320-10_15" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="TGS-560-25_50" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="TGS-560-50_100" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="TGMmini" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="TGMcontroller" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="TGZpMotion" sheetId="23" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="215">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -282,31 +284,61 @@
     <t xml:space="preserve">1 x 4pin MOLEX Micro-lock 50557005011</t>
   </si>
   <si>
+    <t xml:space="preserve">6–48 VDC (abs. Max. 59 VDC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100A</t>
+  </si>
+  <si>
     <t xml:space="preserve">250 A</t>
   </si>
   <si>
     <t xml:space="preserve">70 W</t>
   </si>
   <si>
+    <t xml:space="preserve">DC BUS (+DC, -DC) – na PCB označeno „VCC, GND“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 x Pressfit M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Řízení, STO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin MOLEX Micro-Lock, 5055700501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x Pressfit M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Externí temistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 2pin MOLEX Micro-Fit 3.0, 430250200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin MOLEX Micro-Fit 3.0, 430250400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 22pin WEIDMÜLLER  B2CF 3.50/22/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x zelená (SERVO OK)  1x červená (SERVO ERROR)</t>
+  </si>
+  <si>
     <t xml:space="preserve">8 x Pressfit M5</t>
   </si>
   <si>
     <t xml:space="preserve">1 x 5pin MOLEX Micro-Fit 3.0, 436450500</t>
   </si>
   <si>
-    <t xml:space="preserve">3 x Pressfit M8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 4pin MOLEX Micro-Fit 3.0, 430250400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Externí temistor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 2pin MOLEX Micro-Fit 3.0, 430250200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 A</t>
+    <t xml:space="preserve">2 x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
   </si>
   <si>
     <t xml:space="preserve">425 A</t>
@@ -336,9 +368,6 @@
     <t xml:space="preserve">1 x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
   </si>
   <si>
-    <t xml:space="preserve">1 x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
-  </si>
-  <si>
     <t xml:space="preserve">EMI FILTR</t>
   </si>
   <si>
@@ -366,9 +395,6 @@
     <t xml:space="preserve">2 x 6pin WEIDMÜLLER  SLS 5.08/06/180FI </t>
   </si>
   <si>
-    <t xml:space="preserve">2 x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
-  </si>
-  <si>
     <t xml:space="preserve">400 VAC</t>
   </si>
   <si>
@@ -661,9 +687,6 @@
   </si>
   <si>
     <t xml:space="preserve">Červená/zelená dioda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 22pin WEIDMÜLLER  B2CF 3.50/22/180</t>
   </si>
 </sst>
 </file>
@@ -741,7 +764,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -750,24 +773,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1100,10 +1115,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -1128,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1136,7 +1151,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1144,132 +1159,132 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>107</v>
@@ -1277,18 +1292,23 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>98</v>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1307,229 +1327,195 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>109</v>
+      <c r="B3" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>110</v>
+      <c r="B4" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>111</v>
+      <c r="B5" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-    </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-    </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-    </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>95</v>
+      <c r="B24" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="1" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1548,229 +1534,195 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>109</v>
+      <c r="B3" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>118</v>
+      <c r="B4" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>119</v>
+      <c r="B5" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-    </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-    </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-    </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>95</v>
+      <c r="B24" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="1" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1797,221 +1749,221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>117</v>
+      <c r="B30" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2038,221 +1990,221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="B30" s="2" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2271,216 +2223,229 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2499,182 +2464,229 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="6"/>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="6"/>
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="6"/>
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="6"/>
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="6"/>
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="6"/>
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="6"/>
+      <c r="A8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="6"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>161</v>
-      </c>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>161</v>
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>169</v>
+      <c r="A22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2693,12 +2705,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2710,154 +2721,136 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>155</v>
+      <c r="A10" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C10" s="6"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>157</v>
+      <c r="A11" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="6"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>163</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>1</v>
@@ -2865,18 +2858,63 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>169</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2895,7 +2933,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2912,98 +2950,98 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="6"/>
+      <c r="A2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6"/>
+      <c r="A3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="6"/>
+      <c r="A4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="6"/>
+      <c r="A5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="6"/>
+      <c r="A6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="6"/>
+      <c r="A7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C8" s="6"/>
+      <c r="A8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6"/>
+      <c r="A9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
@@ -3011,18 +3049,18 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3038,12 +3076,12 @@
         <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>1</v>
@@ -3051,50 +3089,26 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3113,7 +3127,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -3130,122 +3144,122 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C12" s="6"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="6"/>
+      <c r="A13" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>169</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C15" s="6"/>
+        <v>169</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
@@ -3253,26 +3267,50 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>205</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3506,7 +3544,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -3523,151 +3561,189 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>184</v>
+      <c r="A2" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="6"/>
+        <v>178</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="6"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="6"/>
+      <c r="A14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>203</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>98</v>
+      <c r="A20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3686,6 +3762,364 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3704,33 +4138,33 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="6"/>
+        <v>193</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="6"/>
+        <v>195</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="6"/>
+        <v>193</v>
+      </c>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="6"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -3739,7 +4173,7 @@
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -3748,7 +4182,7 @@
       <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -3757,7 +4191,7 @@
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -3766,19 +4200,19 @@
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="6"/>
+        <v>204</v>
+      </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="6"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -3787,35 +4221,35 @@
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="6"/>
+        <v>214</v>
+      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="6"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3823,7 +4257,7 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>207</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -4199,7 +4633,7 @@
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4219,10 +4653,6 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-    </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>0</v>
@@ -4232,18 +4662,18 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4256,7 +4686,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -4264,7 +4694,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -4287,203 +4717,251 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>53</v>
+      <c r="B5" s="0" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>80</v>
+      <c r="B6" s="0" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="B7" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
+      <c r="B10" s="0" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
+      <c r="B11" s="0" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="B12" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>25</v>
+      <c r="A15" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B23" s="0" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B24" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="B30" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="B31" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>87</v>
+      <c r="B33" s="0" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4502,7 +4980,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -4510,195 +4988,243 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>53</v>
+      <c r="B5" s="0" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>87</v>
+      <c r="B33" s="0" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4769,7 +5295,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4777,7 +5303,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4825,7 +5351,7 @@
         <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4849,7 +5375,7 @@
         <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4865,7 +5391,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4873,15 +5399,15 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>84</v>
+      <c r="B24" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4889,7 +5415,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4897,7 +5423,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4905,15 +5431,15 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -4932,7 +5458,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -4960,7 +5486,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4968,7 +5494,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4976,7 +5502,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4984,7 +5510,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4992,7 +5518,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5080,7 +5606,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5088,44 +5614,47 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>96</v>
+      <c r="B24" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>98</v>
+      <c r="B27" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>101</v>
+        <v>89</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -5144,10 +5673,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -5172,7 +5701,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5180,7 +5709,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5188,135 +5717,135 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>95</v>
+        <v>36</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5324,7 +5853,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5332,7 +5861,15 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="229">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -53,276 +53,294 @@
     <t xml:space="preserve">Ovládací napětí</t>
   </si>
   <si>
+    <t xml:space="preserve">24 VDC ± 10 %, 400 mA*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výkonové napájecí napětí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–48 VDC (jištění 30A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalovaný příkon pro provoz S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trvalý proud na jednu osu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trvalý celkový proud při provozu dvou os</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 15 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximální výstupní proud (max. 5 s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 30 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ztráty při jmenovité zátěži</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stupeň krytí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOMUNIKACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4pin WEIDMÜLLER  B2CF 3.50/04/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETHERCAT IN/OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100/1000 Mb/s, 2x RJ45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETHERNET UDP (servis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100/1000 Mb/s, RJ45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vstupy/výstupy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 AI, 8 DI, 6 DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x 22pin WEIDMÜLLER  B2CF 3.50/22/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIGNALIZACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED displej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chybové hlášení, 2x7 segment LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED signalizace (osa 1 a 2 zvlášť)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x zelená (SERVO OK)  1x červená (SERVO ERROR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTATNÍ KONEKTORY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Napájení výkonové části</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 2pin PHOENIX PC 5/2 2-STCL1-7,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Napájení řídicí části</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorový konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 6pin WEIDMÜLLER  BLZP 5.08HC/06/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zpětnovazební konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Externí enkodér</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–48 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,8 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 50 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 100 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 3pin WAGO push-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WAGO push-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brzdový konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 × 6pin WEIDMÜLLER  BLF 5.00HC/06/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,4 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED signalizace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x Erni šroubovací svorky M5 PRESSFIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin MOLEX micro-lock, 505570-0501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x Erni šroubovací svorky M5 PRESSFIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin MOLEX micro-lock, 505570-0501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100/1000 Mb/s, 2 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100/1000 Mb/s, 1 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I/O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 DI, 6 DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 18pin MOLEX 5031491800 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 DI (TTL), 1 AI, 2 PT1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin MOLEX 5031491200 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEEDBACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB1, FB2, FB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x 10pin MOLEX 5031481090 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin MOLEX 5031481290 CLIK-MATE 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC BUS (+DC, -DC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x Pressfit M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Řízení, STO, BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin MOLEX micro-lock, 5055700501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x Pressfit M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Externí teplota, Brzda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin MOLEX Micro-lock 50557005011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 VDC ± 10 %, 1 A*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–48 VDC (abs. max. 59 VDC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC BUS (+DC, -DC) – na PCB označeno „VCC, GND“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 x Pressfit M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Řízení, STO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin MOLEX Micro-Lock, 5055700501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x Pressfit M8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Externí temistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 2pin MOLEX Micro-Fit 3.0, 430250200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin MOLEX Micro-Fit 3.0, 430250400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6–48 VDC (abs. Max. 59 VDC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 A</t>
+  </si>
+  <si>
     <t xml:space="preserve">24 VDC ± 10 %, 500 mA*</t>
   </si>
   <si>
-    <t xml:space="preserve">Výkonové napájecí napětí</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6–48 VDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalovaný příkon pro provoz S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trvalý proud na jednu osu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trvalý celkový proud při provozu dvou os</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 15 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximální výstupní proud (max. 5 s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 30 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ztráty při jmenovité zátěži</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOMUNIKACE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4pin WEIDMÜLLER  B2CF 3.50/04/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETHERCAT IN/OUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100/1000 Mb/s, 2x RJ45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETHERNET UDP (servis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100/1000 Mb/s, RJ45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vstupy/výstupy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 AI, 8 DI, 6 DO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x 22pin WEIDMÜLLER  B2CF 3.50/22/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIGNALIZACE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED displej</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chybové hlášení, 2x7 segment LED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED signalizace (osa 1 a 2 zvlášť)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x zelená (SERVO OK)  1x červená (SERVO ERROR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTATNÍ KONEKTORY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Napájení výkonové části</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 2pin PHOENIX PC 5/2 2-STCL1-7,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Napájení řídicí části</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorový konektor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 6pin WEIDMÜLLER  BLZP 5.08HC/06/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zpětnovazební konektor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x 8pin WEIDMÜLLER  B2CF 3.50/08/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Externí enkodér</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,8 kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 50 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 100 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 3pin WAGO push-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 4pin WAGO push-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brzdový konektor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 × 6pin WEIDMÜLLER  BLF 5.00HC/06/180F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,4 kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED signalizace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x Erni šroubovací svorky M5 PRESSFIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 5pin MOLEX micro-lock, 505570-0501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 x Erni šroubovací svorky M5 PRESSFIT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 4pin MOLEX micro-lock, 505570-0501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100/1000 Mb/s, 2 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100/1000 Mb/s, 1 x 8pin MOLEX 5031490800 CLIK-MATE 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I/O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 DI, 6 DO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 18pin MOLEX 5031491800 CLIK-MATE 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 DI (TTL), 1 AI, 2 PT1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 12pin MOLEX 5031491200 CLIK-MATE 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEEDBACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB1, FB2, FB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 x 10pin MOLEX 5031481090 CLIK-MATE 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 12pin MOLEX 5031481290 CLIK-MATE 1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC BUS (+DC, -DC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x Pressfit M5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Řízení, STO, BR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 5pin MOLEX micro-lock, 5055700501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 x Pressfit M5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Externí teplota, Brzda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 4pin MOLEX Micro-lock 50557005011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6–48 VDC (abs. Max. 59 VDC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC BUS (+DC, -DC) – na PCB označeno „VCC, GND“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 x Pressfit M8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Řízení, STO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 5pin MOLEX Micro-Lock, 5055700501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 x Pressfit M8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Externí temistor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 2pin MOLEX Micro-Fit 3.0, 430250200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 4pin MOLEX Micro-Fit 3.0, 430250400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 x 22pin WEIDMÜLLER  B2CF 3.50/22/180</t>
   </si>
   <si>
@@ -344,6 +362,9 @@
     <t xml:space="preserve">425 A</t>
   </si>
   <si>
+    <t xml:space="preserve">24 VDC ± 10 %, 700 mA*</t>
+  </si>
+  <si>
     <t xml:space="preserve">230 VAC</t>
   </si>
   <si>
@@ -377,7 +398,10 @@
     <t xml:space="preserve">NLMO62P72-04 nebo NLA062P72-04  </t>
   </si>
   <si>
-    <t xml:space="preserve">140-320 VDC</t>
+    <t xml:space="preserve">24 VDC ± 10 %, 600 mA*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-320 VDC (pojistka 10 A)</t>
   </si>
   <si>
     <t xml:space="preserve">2,6 kW</t>
@@ -395,7 +419,10 @@
     <t xml:space="preserve">2 x 6pin WEIDMÜLLER  SLS 5.08/06/180FI </t>
   </si>
   <si>
-    <t xml:space="preserve">400 VAC</t>
+    <t xml:space="preserve">0-320 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400 VAC/50Hz 6A</t>
   </si>
   <si>
     <t xml:space="preserve">1,7 kW</t>
@@ -422,12 +449,18 @@
     <t xml:space="preserve">NCZXX3P49-04</t>
   </si>
   <si>
+    <t xml:space="preserve">400 VAC/50Hz 10A</t>
+  </si>
+  <si>
     <t xml:space="preserve">3,9 kW</t>
   </si>
   <si>
     <t xml:space="preserve">7 A</t>
   </si>
   <si>
+    <t xml:space="preserve">400 VAC/50Hz 16A</t>
+  </si>
+  <si>
     <t xml:space="preserve">5,6 kW</t>
   </si>
   <si>
@@ -437,6 +470,9 @@
     <t xml:space="preserve">20 A</t>
   </si>
   <si>
+    <t xml:space="preserve">400 VAC/50Hz 20A</t>
+  </si>
+  <si>
     <t xml:space="preserve">8,4 kW</t>
   </si>
   <si>
@@ -452,6 +488,9 @@
     <t xml:space="preserve">10 kHz</t>
   </si>
   <si>
+    <t xml:space="preserve">24 VDC ± 10 %, 2 A*</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-560 VDC</t>
   </si>
   <si>
@@ -600,6 +639,9 @@
   </si>
   <si>
     <t xml:space="preserve">1 x 5pin WEIDMÜLLER BCZ 3.81/05/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 x 400 VAC/50Hz 63A</t>
   </si>
   <si>
     <t xml:space="preserve">150 W</t>
@@ -908,7 +950,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.63"/>
@@ -979,20 +1021,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1011,36 +1053,36 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1051,20 +1093,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1097,6 +1139,14 @@
       </c>
       <c r="B27" s="1" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1115,7 +1165,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -1135,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,7 +1193,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1151,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1159,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1175,23 +1225,23 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1210,60 +1260,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>104</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1271,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1279,7 +1329,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1287,7 +1337,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1295,20 +1345,28 @@
         <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1385,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -1347,7 +1405,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1355,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1363,7 +1421,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1371,7 +1429,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1379,7 +1437,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1387,7 +1445,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1398,20 +1456,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1430,36 +1488,36 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1470,20 +1528,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1491,7 +1549,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1499,7 +1557,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1507,7 +1565,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1515,7 +1573,15 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1600,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -1554,7 +1620,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,7 +1628,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1570,7 +1636,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1578,7 +1644,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1586,7 +1652,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1605,20 +1671,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1637,36 +1703,36 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1677,20 +1743,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1698,7 +1764,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1706,7 +1772,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1714,7 +1780,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1722,7 +1788,15 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1741,7 +1815,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -1761,7 +1835,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1769,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1777,7 +1851,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1785,7 +1859,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1793,7 +1867,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1801,35 +1875,35 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1849,79 +1923,79 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1929,7 +2003,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1937,7 +2011,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1945,25 +2019,33 @@
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1982,7 +2064,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -2002,7 +2084,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2010,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2018,7 +2100,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2026,7 +2108,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2042,35 +2124,35 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2090,79 +2172,79 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2170,7 +2252,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2178,7 +2260,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2186,25 +2268,33 @@
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2223,7 +2313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -2243,7 +2333,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2251,7 +2341,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2259,7 +2349,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2267,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2275,7 +2365,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2283,35 +2373,35 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2331,79 +2421,79 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2411,7 +2501,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2419,7 +2509,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2427,25 +2517,33 @@
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2464,7 +2562,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -2484,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2492,7 +2590,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2500,7 +2598,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2508,7 +2606,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2516,7 +2614,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2524,35 +2622,35 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2572,79 +2670,79 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2652,7 +2750,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2660,7 +2758,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2668,25 +2766,33 @@
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2705,7 +2811,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2725,7 +2831,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2733,7 +2839,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2741,7 +2847,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2749,7 +2855,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2757,7 +2863,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2765,7 +2871,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2773,23 +2879,23 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2808,36 +2914,36 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2848,20 +2954,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2869,7 +2975,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2877,23 +2983,23 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2901,20 +3007,28 @@
         <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>108</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>146</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2933,7 +3047,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -2951,164 +3065,173 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C11" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3127,7 +3250,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -3145,16 +3268,16 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -3163,52 +3286,52 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -3217,89 +3340,90 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C11" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>169</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>185</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>1</v>
@@ -3307,10 +3431,18 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>177</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3329,7 +3461,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.04"/>
@@ -3357,7 +3489,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3365,7 +3497,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3373,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3381,7 +3513,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3389,7 +3521,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3397,23 +3529,23 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3432,36 +3564,36 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3472,20 +3604,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3493,7 +3625,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3501,23 +3633,23 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3526,6 +3658,14 @@
       </c>
       <c r="B28" s="1" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3544,7 +3684,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -3561,189 +3701,206 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>147</v>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>148</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>179</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>169</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>188</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>191</v>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3780,28 +3937,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -3810,7 +3967,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -3819,25 +3976,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -3846,28 +4003,28 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -3876,7 +4033,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -3885,16 +4042,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
@@ -3902,26 +4059,26 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -3958,28 +4115,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -3988,7 +4145,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -3997,25 +4154,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -4024,10 +4181,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -4036,7 +4193,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
@@ -4045,10 +4202,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -4057,7 +4214,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -4066,42 +4223,42 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4138,28 +4295,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -4168,7 +4325,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -4177,25 +4334,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -4204,10 +4361,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -4216,7 +4373,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
@@ -4225,10 +4382,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -4237,7 +4394,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -4246,18 +4403,18 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4276,7 +4433,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -4304,7 +4461,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4312,7 +4469,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4320,7 +4477,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4328,7 +4485,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4336,23 +4493,23 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4371,60 +4528,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4432,7 +4589,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4440,23 +4597,23 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,6 +4622,14 @@
       </c>
       <c r="B27" s="1" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4483,7 +4648,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -4511,7 +4676,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4519,7 +4684,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4527,7 +4692,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4535,7 +4700,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4543,23 +4708,23 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4567,7 +4732,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4575,130 +4740,138 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2"/>
+      <c r="A17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>69</v>
+      <c r="A19" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>1</v>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4717,251 +4890,235 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="51.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>3</v>
+      <c r="B2" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>80</v>
+      <c r="B3" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>42</v>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>81</v>
+      <c r="B5" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>82</v>
+      <c r="B6" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>83</v>
+      <c r="B7" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>60</v>
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>61</v>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>62</v>
+      <c r="B12" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>1</v>
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>65</v>
+      <c r="A15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="B16" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>1</v>
+      <c r="A17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>70</v>
+      <c r="A19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="B20" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>1</v>
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="0" t="s">
+      <c r="A24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>85</v>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>87</v>
+      <c r="A28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>1</v>
+      <c r="A29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>88</v>
+      <c r="A31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>90</v>
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>91</v>
+      <c r="A33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4980,7 +5137,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -4988,243 +5145,227 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>3</v>
+      <c r="B2" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>80</v>
+      <c r="B3" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>42</v>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>81</v>
+      <c r="B5" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>90</v>
-      </c>
-    </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>91</v>
+      <c r="A33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -5243,7 +5384,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -5263,7 +5404,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5271,7 +5412,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5279,7 +5420,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5287,7 +5428,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5295,7 +5436,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5303,23 +5444,23 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5338,60 +5479,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5399,31 +5540,31 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>88</v>
+      <c r="B24" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5431,15 +5572,23 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5458,7 +5607,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -5478,7 +5627,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5486,7 +5635,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5494,7 +5643,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5502,7 +5651,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5510,7 +5659,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5518,23 +5667,23 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5553,60 +5702,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5614,31 +5763,31 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>88</v>
+      <c r="B24" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5651,10 +5800,18 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>90</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5673,7 +5830,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -5693,7 +5850,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5701,7 +5858,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5709,7 +5866,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5717,7 +5874,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5725,7 +5882,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5733,23 +5890,23 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5768,60 +5925,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5829,31 +5986,31 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>88</v>
+      <c r="B24" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5866,10 +6023,18 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>90</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -31,6 +31,7 @@
     <sheet name="TGMmini" sheetId="21" state="visible" r:id="rId23"/>
     <sheet name="TGMcontroller" sheetId="22" state="visible" r:id="rId24"/>
     <sheet name="TGZpMotion" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="commonHW_DI" sheetId="24" state="visible" r:id="rId26"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="262">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -729,6 +730,105 @@
   </si>
   <si>
     <t xml:space="preserve">Červená/zelená dioda</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> č. vstupu </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> rozsah napětí log. 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> rozsah napětí log. 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nominální vstupní napětí </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> rozsah napájení DI/DO </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> spotřeba v log. 1 (17V) ±20% </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> spotřeba v log. 1 (24V) ±20% </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> vlastní spotřeba v log.1 (28V) ±20% </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nominální vstupní odpor ±20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Přiřazeno k ose </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Max. vstupní frekvence - obdélník </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> # </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U&lt;sub&gt;log0&lt;/sub&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U&lt;sub&gt;log1&lt;/sub&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U&lt;sub&gt;nom&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDD&lt;sub&gt;IO&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I&lt;sub&gt;in17&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I&lt;sub&gt;in24&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I&lt;sub&gt;in28&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RI&lt;sub&gt;inNom&lt;/sub&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Osa č. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> f&lt;sub&gt;maxSq&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> kΩ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-					 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">kHz					 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0-10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17-28V </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17-28V</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nevyžaduje</t>
   </si>
 </sst>
 </file>
@@ -4428,6 +4528,462 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="26.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30.23"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0"/>
+      <c r="B15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/Manual/source/CZ/tab/parameters.xlsx
+++ b/Manual/source/CZ/tab/parameters.xlsx
@@ -32,6 +32,8 @@
     <sheet name="TGMcontroller" sheetId="22" state="visible" r:id="rId24"/>
     <sheet name="TGZpMotion" sheetId="23" state="visible" r:id="rId25"/>
     <sheet name="commonHW_DI" sheetId="24" state="visible" r:id="rId26"/>
+    <sheet name="commonHW_DO" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="commonHW_AI" sheetId="26" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="285">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -768,13 +770,13 @@
     <t xml:space="preserve"> # </t>
   </si>
   <si>
-    <t xml:space="preserve"> U&lt;sub&gt;log0&lt;/sub&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> U&lt;sub&gt;log1&lt;/sub&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> U&lt;sub&gt;nom&lt;/sub&gt;</t>
+    <t xml:space="preserve"> V&lt;sub&gt;log0&lt;/sub&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V&lt;sub&gt;log1&lt;/sub&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V&lt;sub&gt;nom&lt;/sub&gt;</t>
   </si>
   <si>
     <t xml:space="preserve"> VDD&lt;sub&gt;IO&lt;/sub&gt;</t>
@@ -789,46 +791,141 @@
     <t xml:space="preserve"> I&lt;sub&gt;in28&lt;/sub&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve"> RI&lt;sub&gt;inNom&lt;/sub&gt; </t>
+    <t xml:space="preserve"> R&lt;sub&gt;in,Nom&lt;/sub&gt; </t>
   </si>
   <si>
     <t xml:space="preserve"> Osa č. </t>
   </si>
   <si>
+    <t xml:space="preserve"> f&lt;sub&gt;max,Sq&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> kΩ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-					 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">kHz					 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0-10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17-28V </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17-28V</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nevyžaduje</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> č. výstupu </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nominální výstupní napětí </t>
+  </si>
+  <si>
+    <t xml:space="preserve">min. napájecí napětí </t>
+  </si>
+  <si>
+    <t xml:space="preserve">max. napájecí napětí 𐠒 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">min.výstupní napětí ±20% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">max. výstupní napětí ±20% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">max. výstupní proud</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> přiřazeno k ose </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> max. frekvence - obdélník </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDD&lt;sub&gt;IO,min&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDD&lt;sub&gt;IO,max&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V&lt;sub&gt;O,min&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V&lt;sub&gt;O,max&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I&lt;sub&gt;O,max&lt;/sub&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve"> f&lt;sub&gt;maxSq&lt;/sub&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> V</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> V </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> mA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> kΩ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">-					 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">kHz					 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0-10 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 17-28V </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 17-28V</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> nevyžaduje</t>
+    <t xml:space="preserve"> VDD&lt;sub&gt;IO&lt;/sub&gt; - 0,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> rozsah napětí</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nom. vstupní odpor ±10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">časová konstanta ±10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V&lt;sub&gt;in&lt;/sub&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R&lt;sub&gt;inNom&lt;/sub&gt; </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">τ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">&lt;sub&gt;in&lt;/sub&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">us</t>
   </si>
 </sst>
 </file>
@@ -838,7 +935,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -862,6 +959,12 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4533,445 +4636,822 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="26.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0"/>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="0"/>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="26.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="27.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>236</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>237</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>238</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>239</v>
+      <c r="B1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>247</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="K2" s="0" t="s">
-        <v>250</v>
+      <c r="B2" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="I3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="J3" s="0" t="s">
-        <v>256</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>257</v>
+      <c r="D3" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>50</v>
+      <c r="C4" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I10" s="0" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>259</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H11" s="0" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I11" s="0" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0"/>
-      <c r="B15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
-      <c r="B18" s="0"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0"/>
-      <c r="B19" s="0"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0"/>
-      <c r="B20" s="0"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
+      <c r="C5" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
